--- a/source/8、绩效异常岗位/5、封包岗/封包岗-5月.xlsx
+++ b/source/8、绩效异常岗位/5、封包岗/封包岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4690" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5054" uniqueCount="189">
   <si>
     <t>数据日期</t>
   </si>
@@ -590,6 +590,12 @@
   </si>
   <si>
     <t>104.3</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H961"/>
+  <dimension ref="A1:H1034"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -26513,6 +26519,1904 @@
       </c>
       <c r="H961" s="1">
         <v>12.2</v>
+      </c>
+    </row>
+    <row r="962" customHeight="1" spans="1:8">
+      <c r="A962" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C962" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D962" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E962" s="1">
+        <v>97.8</v>
+      </c>
+      <c r="F962" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="G962" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H962" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="963" customHeight="1" spans="1:8">
+      <c r="A963" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C963" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D963" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E963" s="1">
+        <v>76.8</v>
+      </c>
+      <c r="F963" s="1">
+        <v>26.4</v>
+      </c>
+      <c r="G963" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H963" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="964" customHeight="1" spans="1:8">
+      <c r="A964" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C964" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D964" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E964" s="1">
+        <v>86.6</v>
+      </c>
+      <c r="F964" s="1">
+        <v>25.1</v>
+      </c>
+      <c r="G964" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H964" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="965" customHeight="1" spans="1:8">
+      <c r="A965" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C965" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D965" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E965" s="1">
+        <v>119</v>
+      </c>
+      <c r="F965" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="G965" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H965" s="1">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="966" customHeight="1" spans="1:8">
+      <c r="A966" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C966" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D966" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E966" s="1">
+        <v>97.4</v>
+      </c>
+      <c r="F966" s="1">
+        <v>22.3</v>
+      </c>
+      <c r="G966" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H966" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="967" customHeight="1" spans="1:8">
+      <c r="A967" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C967" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D967" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E967" s="1">
+        <v>92.7</v>
+      </c>
+      <c r="F967" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="G967" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H967" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="968" customHeight="1" spans="1:8">
+      <c r="A968" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C968" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D968" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E968" s="1">
+        <v>70</v>
+      </c>
+      <c r="F968" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="G968" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H968" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="969" customHeight="1" spans="1:8">
+      <c r="A969" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C969" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D969" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E969" s="1">
+        <v>77.4</v>
+      </c>
+      <c r="F969" s="1">
+        <v>18.4</v>
+      </c>
+      <c r="G969" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H969" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="970" customHeight="1" spans="1:8">
+      <c r="A970" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C970" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D970" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E970" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="F970" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="G970" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H970" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="971" customHeight="1" spans="1:8">
+      <c r="A971" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C971" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D971" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E971" s="1">
+        <v>68.2</v>
+      </c>
+      <c r="F971" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="G971" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H971" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="972" customHeight="1" spans="1:8">
+      <c r="A972" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C972" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D972" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E972" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F972" s="1">
+        <v>18</v>
+      </c>
+      <c r="G972" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H972" s="1">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="973" customHeight="1" spans="1:8">
+      <c r="A973" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C973" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D973" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E973" s="1">
+        <v>91.4</v>
+      </c>
+      <c r="F973" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="G973" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H973" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="974" customHeight="1" spans="1:8">
+      <c r="A974" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C974" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D974" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E974" s="1">
+        <v>113.2</v>
+      </c>
+      <c r="F974" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="G974" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H974" s="1">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="975" customHeight="1" spans="1:8">
+      <c r="A975" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C975" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D975" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E975" s="1">
+        <v>81.7</v>
+      </c>
+      <c r="F975" s="1">
+        <v>14.1</v>
+      </c>
+      <c r="G975" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H975" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="976" customHeight="1" spans="1:8">
+      <c r="A976" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C976" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D976" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E976" s="1">
+        <v>113.8</v>
+      </c>
+      <c r="F976" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G976" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H976" s="1">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="977" customHeight="1" spans="1:8">
+      <c r="A977" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C977" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D977" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E977" s="1">
+        <v>98.7</v>
+      </c>
+      <c r="F977" s="1">
+        <v>13.7</v>
+      </c>
+      <c r="G977" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H977" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="978" customHeight="1" spans="1:8">
+      <c r="A978" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C978" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D978" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E978" s="1">
+        <v>86.2</v>
+      </c>
+      <c r="F978" s="1">
+        <v>13.1</v>
+      </c>
+      <c r="G978" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H978" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="979" customHeight="1" spans="1:8">
+      <c r="A979" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C979" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D979" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E979" s="1">
+        <v>91</v>
+      </c>
+      <c r="F979" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="G979" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H979" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="980" customHeight="1" spans="1:8">
+      <c r="A980" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C980" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D980" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E980" s="1">
+        <v>163.6</v>
+      </c>
+      <c r="F980" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="G980" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H980" s="1">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="981" customHeight="1" spans="1:8">
+      <c r="A981" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C981" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D981" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E981" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="F981" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="G981" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H981" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="982" customHeight="1" spans="1:8">
+      <c r="A982" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C982" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D982" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E982" s="1">
+        <v>72.6</v>
+      </c>
+      <c r="F982" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="G982" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H982" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="983" customHeight="1" spans="1:8">
+      <c r="A983" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C983" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D983" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E983" s="1">
+        <v>110.6</v>
+      </c>
+      <c r="F983" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G983" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H983" s="1">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="984" customHeight="1" spans="1:8">
+      <c r="A984" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C984" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D984" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E984" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="F984" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G984" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H984" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="985" customHeight="1" spans="1:8">
+      <c r="A985" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C985" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D985" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E985" s="1">
+        <v>132.2</v>
+      </c>
+      <c r="F985" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="G985" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H985" s="1">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="986" customHeight="1" spans="1:8">
+      <c r="A986" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C986" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D986" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E986" s="1">
+        <v>89.4</v>
+      </c>
+      <c r="F986" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="G986" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H986" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="987" customHeight="1" spans="1:8">
+      <c r="A987" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C987" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D987" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E987" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="F987" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="G987" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H987" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="988" customHeight="1" spans="1:8">
+      <c r="A988" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C988" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D988" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E988" s="1">
+        <v>122.1</v>
+      </c>
+      <c r="F988" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="G988" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H988" s="1">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="989" customHeight="1" spans="1:8">
+      <c r="A989" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C989" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D989" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E989" s="1">
+        <v>114.3</v>
+      </c>
+      <c r="F989" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="G989" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H989" s="1">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="990" customHeight="1" spans="1:8">
+      <c r="A990" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C990" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D990" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E990" s="1">
+        <v>118.2</v>
+      </c>
+      <c r="F990" s="1">
+        <v>9.2</v>
+      </c>
+      <c r="G990" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H990" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="991" customHeight="1" spans="1:8">
+      <c r="A991" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C991" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D991" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E991" s="1">
+        <v>114</v>
+      </c>
+      <c r="F991" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="G991" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H991" s="1">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="992" customHeight="1" spans="1:8">
+      <c r="A992" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C992" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D992" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E992" s="1">
+        <v>121.9</v>
+      </c>
+      <c r="F992" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G992" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H992" s="1">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="993" customHeight="1" spans="1:8">
+      <c r="A993" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C993" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D993" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E993" s="1">
+        <v>125.9</v>
+      </c>
+      <c r="F993" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G993" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H993" s="1">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="994" customHeight="1" spans="1:8">
+      <c r="A994" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C994" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D994" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E994" s="1">
+        <v>110</v>
+      </c>
+      <c r="F994" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G994" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H994" s="1">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="995" customHeight="1" spans="1:8">
+      <c r="A995" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C995" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D995" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E995" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="F995" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G995" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H995" s="1">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="996" customHeight="1" spans="1:8">
+      <c r="A996" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C996" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D996" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E996" s="1">
+        <v>110</v>
+      </c>
+      <c r="F996" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G996" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H996" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="997" customHeight="1" spans="1:8">
+      <c r="A997" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C997" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D997" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E997" s="1">
+        <v>115.2</v>
+      </c>
+      <c r="F997" s="1">
+        <v>4.4</v>
+      </c>
+      <c r="G997" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H997" s="1">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="998" customHeight="1" spans="1:8">
+      <c r="A998" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C998" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D998" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E998" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="F998" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G998" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H998" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="999" customHeight="1" spans="1:8">
+      <c r="A999" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C999" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D999" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E999" s="1">
+        <v>97.6</v>
+      </c>
+      <c r="F999" s="1">
+        <v>27.1</v>
+      </c>
+      <c r="G999" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H999" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1000" customHeight="1" spans="1:8">
+      <c r="A1000" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1000" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1000" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1000" s="1">
+        <v>76.5</v>
+      </c>
+      <c r="F1000" s="1">
+        <v>25.9</v>
+      </c>
+      <c r="G1000" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1000" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1001" customHeight="1" spans="1:8">
+      <c r="A1001" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1001" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1001" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1001" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="F1001" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="G1001" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1001" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1002" customHeight="1" spans="1:8">
+      <c r="A1002" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1002" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1002" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1002" s="1">
+        <v>97.4</v>
+      </c>
+      <c r="F1002" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="G1002" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1002" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1003" customHeight="1" spans="1:8">
+      <c r="A1003" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1003" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1003" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1003" s="1">
+        <v>118.6</v>
+      </c>
+      <c r="F1003" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="G1003" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1003" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1004" customHeight="1" spans="1:8">
+      <c r="A1004" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1004" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1004" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1004" s="1">
+        <v>92.3</v>
+      </c>
+      <c r="F1004" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="G1004" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1004" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1005" customHeight="1" spans="1:8">
+      <c r="A1005" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1005" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1005" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1005" s="1">
+        <v>69.9</v>
+      </c>
+      <c r="F1005" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="G1005" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1005" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1006" customHeight="1" spans="1:8">
+      <c r="A1006" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1006" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1006" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1006" s="1">
+        <v>85</v>
+      </c>
+      <c r="F1006" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="G1006" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1006" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1007" customHeight="1" spans="1:8">
+      <c r="A1007" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1007" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1007" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1007" s="1">
+        <v>77.5</v>
+      </c>
+      <c r="F1007" s="1">
+        <v>18.6</v>
+      </c>
+      <c r="G1007" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1007" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1008" customHeight="1" spans="1:8">
+      <c r="A1008" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1008" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1008" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1008" s="1">
+        <v>107.9</v>
+      </c>
+      <c r="F1008" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="G1008" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1008" s="1">
+        <v>8.2</v>
+      </c>
+    </row>
+    <row r="1009" customHeight="1" spans="1:8">
+      <c r="A1009" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1009" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1009" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1009" s="1">
+        <v>67.9</v>
+      </c>
+      <c r="F1009" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="G1009" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1009" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1010" customHeight="1" spans="1:8">
+      <c r="A1010" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1010" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1010" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1010" s="1">
+        <v>113.1</v>
+      </c>
+      <c r="F1010" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="G1010" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1010" s="1">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1011" customHeight="1" spans="1:8">
+      <c r="A1011" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1011" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1011" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1011" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="F1011" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="G1011" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1011" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1012" customHeight="1" spans="1:8">
+      <c r="A1012" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1012" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1012" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1012" s="1">
+        <v>81.5</v>
+      </c>
+      <c r="F1012" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G1012" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1012" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1013" customHeight="1" spans="1:8">
+      <c r="A1013" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1013" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1013" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1013" s="1">
+        <v>113.8</v>
+      </c>
+      <c r="F1013" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G1013" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1013" s="1">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1014" customHeight="1" spans="1:8">
+      <c r="A1014" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1014" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1014" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1014" s="1">
+        <v>98.7</v>
+      </c>
+      <c r="F1014" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="G1014" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1014" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1015" customHeight="1" spans="1:8">
+      <c r="A1015" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1015" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1015" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1015" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1015" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="F1015" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="G1015" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1015" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1016" customHeight="1" spans="1:8">
+      <c r="A1016" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1016" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1016" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1016" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1016" s="1">
+        <v>163.7</v>
+      </c>
+      <c r="F1016" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="G1016" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1016" s="1">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="1017" customHeight="1" spans="1:8">
+      <c r="A1017" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1017" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1017" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1017" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1017" s="1">
+        <v>90.8</v>
+      </c>
+      <c r="F1017" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="G1017" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1017" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1018" customHeight="1" spans="1:8">
+      <c r="A1018" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1018" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1018" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1018" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1018" s="1">
+        <v>87.4</v>
+      </c>
+      <c r="F1018" s="1">
+        <v>12</v>
+      </c>
+      <c r="G1018" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1018" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1019" customHeight="1" spans="1:8">
+      <c r="A1019" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1019" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1019" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1019" s="1">
+        <v>111.1</v>
+      </c>
+      <c r="F1019" s="1">
+        <v>11.1</v>
+      </c>
+      <c r="G1019" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1019" s="1">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1020" customHeight="1" spans="1:8">
+      <c r="A1020" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1020" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1020" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1020" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1020" s="1">
+        <v>132</v>
+      </c>
+      <c r="F1020" s="1">
+        <v>10.2</v>
+      </c>
+      <c r="G1020" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1020" s="1">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="1021" customHeight="1" spans="1:8">
+      <c r="A1021" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1021" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1021" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1021" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1021" s="1">
+        <v>72.2</v>
+      </c>
+      <c r="F1021" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="G1021" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1021" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1022" customHeight="1" spans="1:8">
+      <c r="A1022" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1022" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1022" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1022" s="1">
+        <v>89.2</v>
+      </c>
+      <c r="F1022" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="G1022" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1022" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1023" customHeight="1" spans="1:8">
+      <c r="A1023" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1023" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1023" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1023" s="1">
+        <v>90</v>
+      </c>
+      <c r="F1023" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="G1023" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1023" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1024" customHeight="1" spans="1:8">
+      <c r="A1024" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1024" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1024" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1024" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1024" s="1">
+        <v>121.5</v>
+      </c>
+      <c r="F1024" s="1">
+        <v>9.8</v>
+      </c>
+      <c r="G1024" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1024" s="1">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="1025" customHeight="1" spans="1:8">
+      <c r="A1025" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1025" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1025" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1025" s="1">
+        <v>118.5</v>
+      </c>
+      <c r="F1025" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="G1025" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1025" s="1">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="1026" customHeight="1" spans="1:8">
+      <c r="A1026" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1026" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1026" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1026" s="1">
+        <v>114.1</v>
+      </c>
+      <c r="F1026" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="G1026" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1026" s="1">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="1027" customHeight="1" spans="1:8">
+      <c r="A1027" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1027" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1027" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1027" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="F1027" s="1">
+        <v>9</v>
+      </c>
+      <c r="G1027" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1027" s="1">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="1028" customHeight="1" spans="1:8">
+      <c r="A1028" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1028" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1028" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1028" s="1">
+        <v>121.7</v>
+      </c>
+      <c r="F1028" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G1028" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1028" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1029" customHeight="1" spans="1:8">
+      <c r="A1029" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1029" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1029" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1029" s="1">
+        <v>125.6</v>
+      </c>
+      <c r="F1029" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G1029" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1029" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1030" customHeight="1" spans="1:8">
+      <c r="A1030" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1030" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1030" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="F1030" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G1030" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1030" s="1">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1031" customHeight="1" spans="1:8">
+      <c r="A1031" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1031" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1031" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>120.1</v>
+      </c>
+      <c r="F1031" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G1031" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1031" s="1">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="1032" customHeight="1" spans="1:8">
+      <c r="A1032" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1032" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1032" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>110</v>
+      </c>
+      <c r="F1032" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G1032" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1032" s="1">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1033" customHeight="1" spans="1:8">
+      <c r="A1033" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1033" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1033" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>115</v>
+      </c>
+      <c r="F1033" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G1033" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1033" s="1">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="1034" customHeight="1" spans="1:8">
+      <c r="A1034" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1034" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1034" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>112</v>
+      </c>
+      <c r="F1034" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1034" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H1034" s="1">
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>
